--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>MSC AINO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>EMMANUEL P 014S</t>
+          <t>MSC AINO FI641A</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>57</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -853,22 +853,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MSC AINO</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>MSC AINO FI641A</t>
+          <t>EMMANUEL P 014S</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -920,22 +920,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>MSC AINO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>MSC AINO FI641A</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -987,22 +987,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>SAO PAULO EXPRESS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>SAO PAULO EXPRESS 2642W</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1121,22 +1121,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS 2642W</t>
+          <t>EMMANUEL P 014S</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>55</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>EMMANUEL P 014S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1523,22 +1523,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MSC AINO</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>MSC AINO FI641A</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1679,17 +1679,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1737,22 +1737,22 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1805,17 +1805,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>47</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1863,22 +1863,22 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>34</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1968,22 +1968,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ONE SERENITY</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>ONE SERENITY 2639E</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1993,12 +1993,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2045,12 +2045,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MOL CHARISMA</t>
+          <t>HYUNDAI SUPREME</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>MOL CHARISMA 239E</t>
+          <t>HYUNDAI SUPREME 160E</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>69</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2102,22 +2102,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ONE DURBAN</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>ONE DURBAN 001E</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2169,22 +2169,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>HMM IVY</t>
+          <t>HMM DUBLIN</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>HMM IVY 006E</t>
+          <t>HMM DUBLIN 020W</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2194,12 +2194,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2236,22 +2236,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>HYUNDAI FORCE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>HYUNDAI FORCE 119E</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2303,22 +2303,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME</t>
+          <t>ONE SYMPHONY</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME 160E</t>
+          <t>ONE SYMPHONY 2643E</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>71</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2437,22 +2437,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE</t>
+          <t>YM WORTHINESS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE 119E</t>
+          <t>YM WORTHINESS 003W</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY</t>
+          <t>MSC PROCIDA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY 2643E</t>
+          <t>MSC PROCIDA FZ641A</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2571,22 +2571,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>RDO ACE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>RDO ACE 2642E</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2027-01-02</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2638,22 +2638,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>YM WORTHINESS</t>
+          <t>ONE MODERN</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>YM WORTHINESS 003W</t>
+          <t>ONE MODERN 083E</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2663,12 +2663,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>69</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2705,22 +2705,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>MSC PROCIDA</t>
+          <t>HYUNDAI FORWARD</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>MSC PROCIDA FZ641A</t>
+          <t>HYUNDAI FORWARD 172E</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>70</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2772,22 +2772,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HMM DUBLIN</t>
+          <t>MOL CHARISMA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>HMM DUBLIN 020W</t>
+          <t>MOL CHARISMA 239E</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2839,22 +2839,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>RDO ACE</t>
+          <t>HMM IVY</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>RDO ACE 2642E</t>
+          <t>HMM IVY 006E</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2027-01-02</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2906,22 +2906,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ONE MODERN</t>
+          <t>YM WORTHINESS</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ONE MODERN 083E</t>
+          <t>YM WORTHINESS 003W</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2983,12 +2983,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HYUNDAI FORWARD</t>
+          <t>HMM VANCOUVER</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>HYUNDAI FORWARD 172E</t>
+          <t>HMM VANCOUVER 308E</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -3040,22 +3040,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>YM WORTHINESS</t>
+          <t>HYUNDAI BRAVE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>YM WORTHINESS 003W</t>
+          <t>HYUNDAI BRAVE 120E</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -3107,22 +3107,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER</t>
+          <t>ONE SERENITY</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER 308E</t>
+          <t>ONE SERENITY 2639E</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -3308,22 +3308,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HYUNDAI BRAVE</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>HYUNDAI BRAVE 120E</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3333,12 +3333,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2027-01-02</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>58</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -3375,22 +3375,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>SEASPAN THAMES</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>SEASPAN THAMES 2644E</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2027-01-02</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>70</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3415,74 +3415,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-10 05:03 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>AX3</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>SEASPAN THAMES</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>SEASPAN THAMES 2644E</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2027-01-15</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>2026-10-10 05:03 UTC</t>
+          <t>2026-10-11 04:52 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -528,12 +528,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:06 UTC</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:06 UTC</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:06 UTC</t>
         </is>
       </c>
     </row>
@@ -719,22 +719,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS 2642W</t>
+          <t>EMMANUEL P 014S</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:06 UTC</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:06 UTC</t>
         </is>
       </c>
     </row>
@@ -853,22 +853,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>SAO PAULO EXPRESS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>EMMANUEL P 014S</t>
+          <t>SAO PAULO EXPRESS 2642W</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:06 UTC</t>
         </is>
       </c>
     </row>
@@ -920,22 +920,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MSC AINO</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>MSC AINO FI641A</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:06 UTC</t>
         </is>
       </c>
     </row>
@@ -987,22 +987,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS 2642W</t>
+          <t>EMMANUEL P 014S</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1121,22 +1121,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>MSC AINO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>EMMANUEL P 014S</t>
+          <t>MSC AINO FI641A</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1188,22 +1188,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>SAO PAULO EXPRESS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>SAO PAULO EXPRESS 2642W</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>EMMANUEL P 014S</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>EMMANUEL P 014S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1533,12 +1533,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>55</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1742,17 +1742,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1926,22 +1926,22 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1968,22 +1968,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>HYUNDAI FORCE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>HYUNDAI FORCE 119E</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1993,12 +1993,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2035,22 +2035,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME</t>
+          <t>YM WORTHINESS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME 160E</t>
+          <t>YM WORTHINESS 003W</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2060,12 +2060,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2102,22 +2102,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>HYUNDAI SUPREME</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>HYUNDAI SUPREME 160E</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>69</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2169,22 +2169,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>HMM DUBLIN</t>
+          <t>MOL COURAGE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>HMM DUBLIN 020W</t>
+          <t>MOL COURAGE 069E</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2194,12 +2194,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>73</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2236,22 +2236,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE 119E</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2303,22 +2303,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY 2643E</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2328,12 +2328,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>HMM DUBLIN</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>HMM DUBLIN 020W</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>65</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2437,22 +2437,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>CTP</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>YM WORTHINESS</t>
+          <t>WAN HAI 331</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>YM WORTHINESS 003W</t>
+          <t>WAN HAI 331 0030S</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>69</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2504,22 +2504,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MSC PROCIDA</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>MSC PROCIDA FZ641A</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2571,22 +2571,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>RDO ACE</t>
+          <t>ONE COMPETENCE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>RDO ACE 2642E</t>
+          <t>ONE COMPETENCE 100E</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2027-01-02</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2638,22 +2638,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>ONE MODERN</t>
+          <t>MSC PROCIDA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>ONE MODERN 083E</t>
+          <t>MSC PROCIDA FZ641A</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2663,12 +2663,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2705,22 +2705,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>HYUNDAI FORWARD</t>
+          <t>ONE SERENITY</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>HYUNDAI FORWARD 172E</t>
+          <t>ONE SERENITY 2639E</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2772,22 +2772,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>MOL CHARISMA</t>
+          <t>HMM DUBLIN</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>MOL CHARISMA 239E</t>
+          <t>HMM DUBLIN 020W</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2839,22 +2839,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HMM IVY</t>
+          <t>HMM VANCOUVER</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>HMM IVY 006E</t>
+          <t>HMM VANCOUVER 308E</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2906,22 +2906,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>YM WORTHINESS</t>
+          <t>HYUNDAI FORWARD</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>YM WORTHINESS 003W</t>
+          <t>HYUNDAI FORWARD 172E</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>70</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2983,12 +2983,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER</t>
+          <t>ONE MODERN</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER 308E</t>
+          <t>ONE MODERN 083E</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>71</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:07 UTC</t>
         </is>
       </c>
     </row>
@@ -3040,22 +3040,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>HYUNDAI BRAVE</t>
+          <t>SEASPAN THAMES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>HYUNDAI BRAVE 120E</t>
+          <t>SEASPAN THAMES 2644E</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3065,12 +3065,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>70</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:07 UTC</t>
         </is>
       </c>
     </row>
@@ -3107,22 +3107,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ONE SERENITY</t>
+          <t>YM WORTHINESS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>ONE SERENITY 2639E</t>
+          <t>YM WORTHINESS 003W</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:07 UTC</t>
         </is>
       </c>
     </row>
@@ -3174,22 +3174,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>HMM DUBLIN</t>
+          <t>ONE SYMPHONY</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>HMM DUBLIN 020W</t>
+          <t>ONE SYMPHONY 2643E</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3199,12 +3199,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>71</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:07 UTC</t>
         </is>
       </c>
     </row>
@@ -3241,22 +3241,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CTP</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>WAN HAI 331</t>
+          <t>RDO ACE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>WAN HAI 331 0030S</t>
+          <t>RDO ACE 2642E</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2027-01-02</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:07 UTC</t>
         </is>
       </c>
     </row>
@@ -3308,22 +3308,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>MOL CHARISMA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>MOL CHARISMA 239E</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3333,12 +3333,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2027-01-02</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:07 UTC</t>
         </is>
       </c>
     </row>
@@ -3375,22 +3375,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SEASPAN THAMES</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>SEASPAN THAMES 2644E</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-02</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>58</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3415,7 +3415,74 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-11 04:52 UTC</t>
+          <t>2026-10-12 05:07 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CNTAO→ITSPE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ITSPE</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>QINGDAO, SHANDONG</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>AX4</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>HMM IVY</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>HMM IVY 006E</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>LA SPEZIA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-12-24</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>TRANSSHIPMENT (1)</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-10-12 05:07 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-12 05:06 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -595,12 +595,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-12 05:06 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MSC AINO</t>
+          <t>SAO PAULO EXPRESS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>MSC AINO FI641A</t>
+          <t>SAO PAULO EXPRESS 2642W</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-12 05:06 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -719,22 +719,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>MSC AINO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>EMMANUEL P 014S</t>
+          <t>MSC AINO FI641A</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>57</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-12 05:06 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -786,22 +786,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-12 05:06 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -853,22 +853,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS 2642W</t>
+          <t>EMMANUEL P 014S</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -893,14 +893,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-12 05:06 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>HKHKG→SEGOT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>SEGOT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -930,27 +930,27 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>GOTHENBURG</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>53</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-12 05:06 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>EMMANUEL P 014S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>55</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-12 05:06 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-12 05:06 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1121,22 +1121,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MSC AINO</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>MSC AINO FI641A</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-12 05:06 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS</t>
+          <t>MSC AINO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS 2642W</t>
+          <t>MSC AINO FI641A</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-12 05:06 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1255,22 +1255,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>EMMANUEL P 014S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-12 05:06 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-12 05:06 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1389,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>SAO PAULO EXPRESS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>SAO PAULO EXPRESS 2642W</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-12 05:06 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>EMMANUEL P 014S</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>62</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-12 05:06 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1533,12 +1533,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>EMMANUEL P 014S</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1563,45 +1563,49 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-12 05:06 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>HKHKG→NOOSL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>NOOSL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>JSM</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1611,12 +1615,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1626,45 +1630,49 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-12 05:06 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>HKHKG→NOOSL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>NOOSL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>JSM</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1674,22 +1682,22 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-12 05:06 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1724,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1737,22 +1745,22 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-12 05:06 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1823,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-12 05:06 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1850,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1863,12 +1871,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1878,7 +1886,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-12 05:06 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1913,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1926,111 +1934,107 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-12 05:06 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CNTAO→ITSPE</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ITSPE</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>QINGDAO, SHANDONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>AX4</t>
-        </is>
-      </c>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE 119E</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>ROTTERDAM</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>34</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (1)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-12 05:07 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CNTAO→ITSPE</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ITSPE</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>QINGDAO, SHANDONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2038,111 +2042,103 @@
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>FE3</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>YM WORTHINESS</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>YM WORTHINESS 003W</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>ROTTERDAM</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (1)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-12 05:07 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CNTAO→ITSPE</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ITSPE</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>QINGDAO, SHANDONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>PN3</t>
-        </is>
-      </c>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME 160E</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>ROTTERDAM</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (1)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-12 05:07 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2169,22 +2165,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>MOL COURAGE</t>
+          <t>ONE SERENITY</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>MOL COURAGE 069E</t>
+          <t>ONE SERENITY 2639E</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2194,12 +2190,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>78</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2209,7 +2205,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-12 05:07 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2236,22 +2232,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>MOL COURAGE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>MOL COURAGE 069E</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2261,12 +2257,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>73</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2276,7 +2272,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-12 05:07 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2303,22 +2299,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>HYUNDAI SUPREME</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>HYUNDAI SUPREME 160E</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2328,12 +2324,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>69</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2343,7 +2339,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-12 05:07 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2370,22 +2366,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HMM DUBLIN</t>
+          <t>HMM VANCOUVER</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>HMM DUBLIN 020W</t>
+          <t>HMM VANCOUVER 308E</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2395,7 +2391,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2410,7 +2406,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-12 05:07 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2437,22 +2433,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CTP</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>WAN HAI 331</t>
+          <t>ONE MODERN</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>WAN HAI 331 0030S</t>
+          <t>ONE MODERN 083E</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2462,12 +2458,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>71</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2477,7 +2473,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-12 05:07 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2500,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2514,12 +2510,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>HMM DUBLIN</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>HMM DUBLIN 020W</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2529,12 +2525,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2544,7 +2540,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-12 05:07 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2571,22 +2567,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE 100E</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2596,12 +2592,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2611,7 +2607,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-12 05:07 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2638,22 +2634,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MSC PROCIDA</t>
+          <t>MOL CHARISMA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>MSC PROCIDA FZ641A</t>
+          <t>MOL CHARISMA 239E</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2663,12 +2659,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2678,7 +2674,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-12 05:07 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2705,22 +2701,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ONE SERENITY</t>
+          <t>HYUNDAI FORWARD</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ONE SERENITY 2639E</t>
+          <t>HYUNDAI FORWARD 172E</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2730,12 +2726,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2745,7 +2741,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-12 05:07 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2768,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2782,12 +2778,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HMM DUBLIN</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>HMM DUBLIN 020W</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2797,12 +2793,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2027-01-02</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>58</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2812,7 +2808,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-12 05:07 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2839,22 +2835,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>CTP</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER</t>
+          <t>WAN HAI 331</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER 308E</t>
+          <t>WAN HAI 331 0030S</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2869,7 +2865,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2879,7 +2875,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-12 05:07 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2906,22 +2902,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>HYUNDAI FORWARD</t>
+          <t>MSC PROCIDA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>HYUNDAI FORWARD 172E</t>
+          <t>MSC PROCIDA FZ641A</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2931,12 +2927,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2946,7 +2942,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-12 05:07 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2973,22 +2969,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>ONE MODERN</t>
+          <t>HMM IVY</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>ONE MODERN 083E</t>
+          <t>HMM IVY 006E</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3003,7 +2999,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3013,7 +3009,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-12 05:07 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -3040,22 +3036,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SEASPAN THAMES</t>
+          <t>HMM DUBLIN</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SEASPAN THAMES 2644E</t>
+          <t>HMM DUBLIN 020W</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3065,12 +3061,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>64</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3080,7 +3076,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-12 05:07 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3103,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3117,12 +3113,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>YM WORTHINESS</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>YM WORTHINESS 003W</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3132,12 +3128,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3147,7 +3143,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-12 05:07 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3210,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-12 05:07 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -3241,22 +3237,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>RDO ACE</t>
+          <t>HYUNDAI FORCE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>RDO ACE 2642E</t>
+          <t>HYUNDAI FORCE 119E</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3266,12 +3262,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2027-01-02</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3281,7 +3277,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-12 05:07 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -3308,22 +3304,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>MOL CHARISMA</t>
+          <t>YM WORTHINESS</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>MOL CHARISMA 239E</t>
+          <t>YM WORTHINESS 003W</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3333,12 +3329,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>51</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3348,7 +3344,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-12 05:07 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -3400,12 +3396,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2027-01-02</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3415,7 +3411,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-12 05:07 UTC</t>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -3442,47 +3438,181 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>FE3</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>YM WORTHINESS</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>YM WORTHINESS 003W</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>LA SPEZIA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>TRANSSHIPMENT (1)</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:06 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CNTAO→ITSPE</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ITSPE</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>QINGDAO, SHANDONG</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>AX3</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>RDO ACE</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>RDO ACE 2642E</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>LA SPEZIA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>TRANSSHIPMENT (1)</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:06 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CNTAO→ITSPE</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ITSPE</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>QINGDAO, SHANDONG</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-11-08</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>AX4</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>HMM IVY</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>HMM IVY 006E</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ONE COMPETENCE</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ONE COMPETENCE 100E</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
         <is>
           <t>LA SPEZIA</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2026-12-24</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2027-01-15</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>2026-10-12 05:07 UTC</t>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:06 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,22 +518,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>SAO PAULO EXPRESS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>SAO PAULO EXPRESS 2642W</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>52</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -585,22 +585,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>MSC AINO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>MSC AINO FI641A</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS 2642W</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -719,22 +719,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MSC AINO</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>MSC AINO FI641A</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -786,22 +786,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>53</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>EMMANUEL P 014S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -920,22 +920,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -1054,22 +1054,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>MSC AINO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>MSC AINO FI641A</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -1188,22 +1188,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>MSC AINO</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>MSC AINO FI641A</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>55</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -1255,22 +1255,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS 2642W</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>EMMANUEL P 014S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1533,12 +1533,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>EMMANUEL P 014S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -1590,22 +1590,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>SAO PAULO EXPRESS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>SAO PAULO EXPRESS 2642W</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>47</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1745,22 +1745,22 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1808,22 +1808,22 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1997,22 +1997,22 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2065,17 +2065,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2123,12 +2123,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -2165,22 +2165,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ONE SERENITY</t>
+          <t>MOL COURAGE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>ONE SERENITY 2639E</t>
+          <t>MOL COURAGE 069E</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>71</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -2232,22 +2232,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MOL COURAGE</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>MOL COURAGE 069E</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-02</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>58</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2299,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME 160E</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER</t>
+          <t>HYUNDAI SUPREME</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER 308E</t>
+          <t>HYUNDAI SUPREME 160E</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>69</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ONE MODERN</t>
+          <t>HYUNDAI FORWARD</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>ONE MODERN 083E</t>
+          <t>HYUNDAI FORWARD 172E</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>75</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -2500,22 +2500,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HMM DUBLIN</t>
+          <t>ONE SYMPHONY</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>HMM DUBLIN 020W</t>
+          <t>ONE SYMPHONY 2643E</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>71</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -2567,22 +2567,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>ONE MODERN</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>ONE MODERN 083E</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>71</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -2701,22 +2701,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>HYUNDAI FORWARD</t>
+          <t>MSC PROCIDA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>HYUNDAI FORWARD 172E</t>
+          <t>MSC PROCIDA FZ641A</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -2768,22 +2768,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>HMM IVY</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>HMM IVY 006E</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2027-01-02</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -2835,22 +2835,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CTP</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>WAN HAI 331</t>
+          <t>RDO ACE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>WAN HAI 331 0030S</t>
+          <t>RDO ACE 2642E</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -2902,22 +2902,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MSC PROCIDA</t>
+          <t>HYUNDAI FORCE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>MSC PROCIDA FZ641A</t>
+          <t>HYUNDAI FORCE 119E</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -2969,22 +2969,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HMM IVY</t>
+          <t>YM WORTHINESS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>HMM IVY 006E</t>
+          <t>YM WORTHINESS 003W</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -3036,22 +3036,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>CTP</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>HMM DUBLIN</t>
+          <t>WAN HAI 331</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>HMM DUBLIN 020W</t>
+          <t>WAN HAI 331 0030S</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>62</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>YM WORTHINESS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>YM WORTHINESS 003W</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>51</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -3170,22 +3170,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY</t>
+          <t>ONE COMPETENCE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY 2643E</t>
+          <t>ONE COMPETENCE 100E</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -3237,22 +3237,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE</t>
+          <t>HMM VANCOUVER</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE 119E</t>
+          <t>HMM VANCOUVER 308E</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>65</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>YM WORTHINESS</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>YM WORTHINESS 003W</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>
@@ -3411,208 +3411,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>FE3</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>YM WORTHINESS</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>YM WORTHINESS 003W</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2026-12-17</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>2026-10-13 06:06 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>AX3</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>RDO ACE</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>RDO ACE 2642E</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>2026-10-13 06:06 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2026-11-08</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>AX4</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>ONE COMPETENCE</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>ONE COMPETENCE 100E</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2027-01-15</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-14 04:09 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,22 +518,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS 2642W</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>47</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -719,22 +719,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -863,12 +863,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>53</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>SAO PAULO EXPRESS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>SAO PAULO EXPRESS 2642W</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>52</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1054,22 +1054,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MSC AINO</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>MSC AINO FI641A</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>54</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1322,22 +1322,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>SAO PAULO EXPRESS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>SAO PAULO EXPRESS 2642W</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1389,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1523,22 +1523,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>MSC AINO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>MSC AINO FI641A</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1590,22 +1590,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS 2642W</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1745,12 +1745,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1997,22 +1997,22 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>34</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2060,22 +2060,22 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2123,12 +2123,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>MOL COURAGE</t>
+          <t>ONE MODERN</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>MOL COURAGE 069E</t>
+          <t>ONE MODERN 083E</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2027-01-02</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>YM WORTHINESS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>YM WORTHINESS 003W</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2366,22 +2366,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>CTP</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME</t>
+          <t>WAN HAI 331</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME 160E</t>
+          <t>WAN HAI 331 0030S</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2433,22 +2433,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HYUNDAI FORWARD</t>
+          <t>RDO ACE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>HYUNDAI FORWARD 172E</t>
+          <t>RDO ACE 2642E</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2500,22 +2500,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY 2643E</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2567,22 +2567,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ONE MODERN</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ONE MODERN 083E</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2634,22 +2634,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MOL CHARISMA</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>MOL CHARISMA 239E</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>78</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>MSC PROCIDA</t>
+          <t>ONE SYMPHONY</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>MSC PROCIDA FZ641A</t>
+          <t>ONE SYMPHONY 2643E</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>78</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2768,22 +2768,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HMM IVY</t>
+          <t>YM WORTHINESS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>HMM IVY 006E</t>
+          <t>YM WORTHINESS 003W</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>57</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2835,22 +2835,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>RDO ACE</t>
+          <t>ONE COMPETENCE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>RDO ACE 2642E</t>
+          <t>ONE COMPETENCE 100E</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>75</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2902,22 +2902,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE</t>
+          <t>HYUNDAI SUPREME</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE 119E</t>
+          <t>HYUNDAI SUPREME 160E</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2969,22 +2969,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>YM WORTHINESS</t>
+          <t>HMM IVY</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>YM WORTHINESS 003W</t>
+          <t>HMM IVY 006E</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -3036,22 +3036,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CTP</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>WAN HAI 331</t>
+          <t>MOL CHARISMA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>WAN HAI 331 0030S</t>
+          <t>MOL CHARISMA 239E</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>83</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -3103,22 +3103,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>YM WORTHINESS</t>
+          <t>HYUNDAI FORCE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>YM WORTHINESS 003W</t>
+          <t>HYUNDAI FORCE 119E</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>81</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -3170,22 +3170,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE</t>
+          <t>MSC PROCIDA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE 100E</t>
+          <t>MSC PROCIDA FZ641A</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER</t>
+          <t>HYUNDAI FORWARD</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER 308E</t>
+          <t>HYUNDAI FORWARD 172E</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -3304,22 +3304,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>HMM VANCOUVER</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>HMM VANCOUVER 308E</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>85</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3344,74 +3344,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-14 04:09 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>FE3</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>HMM GDANSK</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>HMM GDANSK 020W</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2026-12-14</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>2026-10-14 04:09 UTC</t>
+          <t>2026-10-15 03:52 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -585,22 +585,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MSC AINO</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>MSC AINO FI641A</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>52</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>MSC AINO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>MSC AINO FI641A</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -786,22 +786,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>SAO PAULO EXPRESS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>SAO PAULO EXPRESS 2642W</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>52</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -863,12 +863,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS 2642W</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1054,22 +1054,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>54</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1188,22 +1188,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>SAO PAULO EXPRESS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>SAO PAULO EXPRESS 2642W</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1255,22 +1255,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>MSC AINO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>MSC AINO FI641A</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1322,22 +1322,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS 2642W</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>59</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1523,22 +1523,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MSC AINO</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>MSC AINO FI641A</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1750,17 +1750,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>34</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1871,22 +1871,22 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1997,22 +1997,22 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2060,22 +2060,22 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ONE MODERN</t>
+          <t>MOL CHARISMA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>ONE MODERN 083E</t>
+          <t>MOL CHARISMA 239E</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>84</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2299,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>CTP</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>YM WORTHINESS</t>
+          <t>WAN HAI 331</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>YM WORTHINESS 003W</t>
+          <t>WAN HAI 331 0030S</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2366,22 +2366,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CTP</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>WAN HAI 331</t>
+          <t>HMM VANCOUVER</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>WAN HAI 331 0030S</t>
+          <t>HMM VANCOUVER 308E</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>85</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2433,22 +2433,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>RDO ACE</t>
+          <t>HMM IVY</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>RDO ACE 2642E</t>
+          <t>HMM IVY 006E</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2500,22 +2500,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>HYUNDAI FORCE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>HYUNDAI FORCE 119E</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>81</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2577,12 +2577,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>YM WORTHINESS</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>YM WORTHINESS 003W</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY</t>
+          <t>RDO ACE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY 2643E</t>
+          <t>RDO ACE 2642E</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2768,22 +2768,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>YM WORTHINESS</t>
+          <t>ONE MODERN</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>YM WORTHINESS 003W</t>
+          <t>ONE MODERN 083E</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2835,22 +2835,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE</t>
+          <t>MSC PROCIDA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE 100E</t>
+          <t>MSC PROCIDA FZ641A</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>69</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2912,12 +2912,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME</t>
+          <t>MOL COURAGE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME 160E</t>
+          <t>MOL COURAGE 069E</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2969,22 +2969,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HMM IVY</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>HMM IVY 006E</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3036,22 +3036,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>MOL CHARISMA</t>
+          <t>YM WORTHINESS</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>MOL CHARISMA 239E</t>
+          <t>YM WORTHINESS 003W</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>57</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3103,22 +3103,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE 119E</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>78</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3170,22 +3170,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>MSC PROCIDA</t>
+          <t>HYUNDAI SUPREME</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>MSC PROCIDA FZ641A</t>
+          <t>HYUNDAI SUPREME 160E</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3237,22 +3237,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>HYUNDAI FORWARD</t>
+          <t>ONE SYMPHONY</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>HYUNDAI FORWARD 172E</t>
+          <t>ONE SYMPHONY 2643E</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3304,22 +3304,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER</t>
+          <t>ONE COMPETENCE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER 308E</t>
+          <t>ONE COMPETENCE 100E</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>75</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-15 03:52 UTC</t>
+          <t>2026-10-16 03:47 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -528,12 +528,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -585,22 +585,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>SAO PAULO EXPRESS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>SAO PAULO EXPRESS 2642W</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>51</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MSC AINO</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>MSC AINO FI641A</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -786,22 +786,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS 2642W</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -853,22 +853,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>MSC AINO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>MSC AINO FI641A</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -920,22 +920,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>47</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>MSC AINO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>MSC AINO FI641A</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1188,22 +1188,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS 2642W</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>59</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MSC AINO</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>MSC AINO FI641A</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>54</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1523,22 +1523,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>SAO PAULO EXPRESS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>SAO PAULO EXPRESS 2642W</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>54</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1750,17 +1750,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1808,22 +1808,22 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1871,22 +1871,22 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1913,18 +1913,18 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1934,22 +1934,22 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>36</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1997,12 +1997,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2060,22 +2060,22 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2123,156 +2123,148 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CNTAO→ITSPE</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ITSPE</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>QINGDAO, SHANDONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>PN3</t>
-        </is>
-      </c>
+          <t>2026-11-15</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>MOL CHARISMA</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>MOL CHARISMA 239E</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>ROTTERDAM</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (1)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CNTAO→ITSPE</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ITSPE</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>QINGDAO, SHANDONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>FE3</t>
-        </is>
-      </c>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>ROTTERDAM</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>53</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (1)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2291,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CTP</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>WAN HAI 331</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>WAN HAI 331 0030S</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2324,12 +2316,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2339,7 +2331,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2358,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2376,12 +2368,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER</t>
+          <t>MOL CHARISMA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER 308E</t>
+          <t>MOL CHARISMA 239E</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2396,7 +2388,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2406,7 +2398,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -2433,22 +2425,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HMM IVY</t>
+          <t>YM WORTHINESS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>HMM IVY 006E</t>
+          <t>YM WORTHINESS 003W</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2458,12 +2450,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2473,7 +2465,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -2500,22 +2492,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE</t>
+          <t>RDO ACE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE 119E</t>
+          <t>RDO ACE 2642E</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2525,12 +2517,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2540,7 +2532,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -2567,22 +2559,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>YM WORTHINESS</t>
+          <t>HMM IVY</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>YM WORTHINESS 003W</t>
+          <t>HMM IVY 006E</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2592,12 +2584,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2607,7 +2599,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -2634,22 +2626,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>CTP</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>WAN HAI 331</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>WAN HAI 331 0030S</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2659,12 +2651,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2674,7 +2666,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -2701,22 +2693,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>RDO ACE</t>
+          <t>ONE COMPETENCE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>RDO ACE 2642E</t>
+          <t>ONE COMPETENCE 100E</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2726,12 +2718,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>75</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2741,7 +2733,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -2768,22 +2760,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>ONE MODERN</t>
+          <t>HYUNDAI FORCE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>ONE MODERN 083E</t>
+          <t>HYUNDAI FORCE 119E</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2793,12 +2785,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>81</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2808,7 +2800,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -2835,22 +2827,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>MSC PROCIDA</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>MSC PROCIDA FZ641A</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2860,12 +2852,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>78</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2875,7 +2867,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2894,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2912,12 +2904,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MOL COURAGE</t>
+          <t>ONE MODERN</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>MOL COURAGE 069E</t>
+          <t>ONE MODERN 083E</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2927,7 +2919,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2942,7 +2934,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2986,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3009,7 +3001,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3028,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3046,12 +3038,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>YM WORTHINESS</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>YM WORTHINESS 003W</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3061,12 +3053,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3076,7 +3068,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -3103,22 +3095,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>MOL COURAGE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>MOL COURAGE 069E</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3128,12 +3120,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3143,7 +3135,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -3170,22 +3162,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME</t>
+          <t>ONE SYMPHONY</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME 160E</t>
+          <t>ONE SYMPHONY 2643E</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3200,7 +3192,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>82</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3210,7 +3202,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -3237,22 +3229,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY</t>
+          <t>HYUNDAI SUPREME</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY 2643E</t>
+          <t>HYUNDAI SUPREME 160E</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3267,7 +3259,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3277,7 +3269,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-16 03:47 UTC</t>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -3304,22 +3296,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE</t>
+          <t>YM WORTHINESS</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE 100E</t>
+          <t>YM WORTHINESS 003W</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3329,22 +3321,89 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>TRANSSHIPMENT (1)</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-10-17 03:37 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CNTAO→ITSPE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ITSPE</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>QINGDAO, SHANDONG</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>PN3</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>HMM VANCOUVER</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>HMM VANCOUVER 308E</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>LA SPEZIA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
           <t>2027-01-22</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>2026-10-16 03:47 UTC</t>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-10-17 03:37 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -719,22 +719,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>52</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -786,22 +786,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>MSC AINO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>MSC AINO FI641A</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -853,22 +853,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MSC AINO</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>MSC AINO FI641A</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>47</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -920,22 +920,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>59</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -1054,22 +1054,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MSC AINO</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>MSC AINO FI641A</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -1121,22 +1121,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>MSC AINO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>MSC AINO FI641A</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>54</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1808,22 +1808,22 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -1913,18 +1913,18 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1934,22 +1934,22 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>53</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1997,12 +1997,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2060,22 +2060,22 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2123,22 +2123,22 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -2165,18 +2165,18 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2264,74 +2264,70 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CNTAO→ITSPE</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ITSPE</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>QINGDAO, SHANDONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>FE3</t>
-        </is>
-      </c>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>ROTTERDAM</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (1)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -2358,22 +2354,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MOL CHARISMA</t>
+          <t>RDO ACE</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>MOL CHARISMA 239E</t>
+          <t>RDO ACE 2642E</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2383,12 +2379,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2398,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -2425,22 +2421,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>YM WORTHINESS</t>
+          <t>ONE COMPETENCE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>YM WORTHINESS 003W</t>
+          <t>ONE COMPETENCE 100E</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2450,7 +2446,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2465,7 +2461,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -2492,22 +2488,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>RDO ACE</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>RDO ACE 2642E</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2522,7 +2518,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2532,7 +2528,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -2559,22 +2555,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>HMM IVY</t>
+          <t>ONE SYMPHONY</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>HMM IVY 006E</t>
+          <t>ONE SYMPHONY 2643E</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2584,12 +2580,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2599,7 +2595,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -2626,22 +2622,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CTP</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>WAN HAI 331</t>
+          <t>HMM VANCOUVER</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>WAN HAI 331 0030S</t>
+          <t>HMM VANCOUVER 308E</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2651,12 +2647,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2666,7 +2662,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -2693,22 +2689,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE</t>
+          <t>MOL CHARISMA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE 100E</t>
+          <t>MOL CHARISMA 239E</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2718,12 +2714,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2733,7 +2729,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -2760,22 +2756,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>CTP</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE</t>
+          <t>WAN HAI 331</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE 119E</t>
+          <t>WAN HAI 331 0030S</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2785,12 +2781,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>65</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2800,7 +2796,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -2827,22 +2823,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>HMM IVY</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>HMM IVY 006E</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2852,12 +2848,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2867,7 +2863,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2890,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2904,12 +2900,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ONE MODERN</t>
+          <t>HYUNDAI SUPREME</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ONE MODERN 083E</t>
+          <t>HYUNDAI SUPREME 160E</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2919,7 +2915,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2934,7 +2930,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -2961,22 +2957,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>CONTI CONTESSA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>CONTI CONTESSA 027E</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2986,12 +2982,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3001,7 +2997,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -3053,12 +3049,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3068,7 +3064,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -3095,22 +3091,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>MOL COURAGE</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>MOL COURAGE 069E</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3120,12 +3116,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3135,7 +3131,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -3162,22 +3158,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY</t>
+          <t>HYUNDAI FORCE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY 2643E</t>
+          <t>HYUNDAI FORCE 119E</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3187,12 +3183,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>73</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3202,7 +3198,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3225,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3239,12 +3235,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME</t>
+          <t>ONE MODERN</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME 160E</t>
+          <t>ONE MODERN 083E</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3254,12 +3250,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3269,7 +3265,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -3296,22 +3292,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>YM WORTHINESS</t>
+          <t>MOL COURAGE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>YM WORTHINESS 003W</t>
+          <t>MOL COURAGE 069E</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3321,12 +3317,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3336,7 +3332,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>
@@ -3363,22 +3359,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER 308E</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3388,12 +3384,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3403,7 +3399,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-17 03:37 UTC</t>
+          <t>2026-10-18 03:44 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,22 +518,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>SAO PAULO EXPRESS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>SAO PAULO EXPRESS 2642W</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -595,12 +595,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS</t>
+          <t>MSC AINO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS 2642W</t>
+          <t>MSC AINO FI641A</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>51</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>47</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -786,22 +786,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MSC AINO</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>MSC AINO FI641A</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -863,12 +863,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -920,22 +920,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>52</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -987,22 +987,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>MSC AINO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>MSC AINO FI641A</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1054,22 +1054,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1121,22 +1121,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MSC AINO</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>MSC AINO FI641A</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>54</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1255,22 +1255,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>54</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1322,22 +1322,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>SAO PAULO EXPRESS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>SAO PAULO EXPRESS 2642W</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1523,22 +1523,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS 2642W</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>59</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1745,22 +1745,22 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1808,22 +1808,22 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1876,17 +1876,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1997,12 +1997,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2039,18 +2039,18 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2060,12 +2060,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2123,22 +2123,22 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2165,18 +2165,18 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>53</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2264,70 +2264,74 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>FE3</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>70</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2398,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2425,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2431,12 +2435,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE</t>
+          <t>HYUNDAI FORCE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE 100E</t>
+          <t>HYUNDAI FORCE 119E</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2451,7 +2455,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>73</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2461,7 +2465,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2492,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2498,12 +2502,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>HMM SOUTHAMPTON</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>HMM SOUTHAMPTON 020W</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2513,12 +2517,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2528,7 +2532,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2555,22 +2559,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY</t>
+          <t>HMM VANCOUVER</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY 2643E</t>
+          <t>HMM VANCOUVER 308E</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2585,7 +2589,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2595,7 +2599,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2627,17 +2631,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER 308E</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2647,12 +2651,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2662,7 +2666,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2689,22 +2693,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>MOL CHARISMA</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>MOL CHARISMA 239E</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2714,12 +2718,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2729,7 +2733,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2756,22 +2760,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CTP</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>WAN HAI 331</t>
+          <t>HMM IVY</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>WAN HAI 331 0030S</t>
+          <t>HMM IVY 006E</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2781,12 +2785,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2796,7 +2800,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2827,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2833,12 +2837,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HMM IVY</t>
+          <t>CONTI CONTESSA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>HMM IVY 006E</t>
+          <t>CONTI CONTESSA 027E</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2848,12 +2852,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2863,7 +2867,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2890,22 +2894,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME</t>
+          <t>ONE SYMPHONY</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME 160E</t>
+          <t>ONE SYMPHONY 2643E</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2920,7 +2924,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>75</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2930,7 +2934,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2957,22 +2961,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CONTI CONTESSA</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>CONTI CONTESSA 027E</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2982,12 +2986,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2997,7 +3001,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -3024,22 +3028,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>CTP</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>WAN HAI 331</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>WAN HAI 331 0030S</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3049,12 +3053,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>65</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3064,7 +3068,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -3091,22 +3095,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>MOL COURAGE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>MOL COURAGE 069E</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3116,12 +3120,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3131,7 +3135,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -3158,22 +3162,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE</t>
+          <t>MOL CHARISMA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE 119E</t>
+          <t>MOL CHARISMA 239E</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3188,7 +3192,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3198,7 +3202,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -3225,22 +3229,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ONE MODERN</t>
+          <t>ONE COMPETENCE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ONE MODERN 083E</t>
+          <t>ONE COMPETENCE 100E</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3250,12 +3254,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3265,7 +3269,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3296,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3302,12 +3306,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>MOL COURAGE</t>
+          <t>HYUNDAI SUPREME</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>MOL COURAGE 069E</t>
+          <t>HYUNDAI SUPREME 160E</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3317,7 +3321,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3332,7 +3336,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3363,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3369,12 +3373,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>HMM SOUTHAMPTON</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>HMM SOUTHAMPTON 020W</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3384,12 +3388,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>59</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3399,7 +3403,74 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-18 03:44 UTC</t>
+          <t>2026-10-19 03:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CNTAO→ITSPE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ITSPE</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>QINGDAO, SHANDONG</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>PN3</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ONE MODERN</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ONE MODERN 083E</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>LA SPEZIA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>TRANSSHIPMENT (1)</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-10-19 03:54 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,22 +518,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS 2642W</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -595,12 +595,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MSC AINO</t>
+          <t>SAO PAULO EXPRESS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>MSC AINO FI641A</t>
+          <t>SAO PAULO EXPRESS 2642W</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>MSC AINO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>MSC AINO FI641A</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>57</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -853,22 +853,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>51</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -987,22 +987,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MSC AINO</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>MSC AINO FI641A</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1054,22 +1054,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1255,22 +1255,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>MSC AINO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>MSC AINO FI641A</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>51</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1322,22 +1322,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS 2642W</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>51</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>61</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>54</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1523,22 +1523,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>SAO PAULO EXPRESS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>SAO PAULO EXPRESS 2642W</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1657,22 +1657,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>47</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1934,22 +1934,22 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1997,12 +1997,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2039,18 +2039,18 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2060,22 +2060,22 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2102,18 +2102,18 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2123,12 +2123,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2291,22 +2291,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>MOL COURAGE</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>MOL COURAGE 069E</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>69</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2358,22 +2358,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>RDO ACE</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>RDO ACE 2642E</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>70</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2435,12 +2435,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE</t>
+          <t>ONE COMPETENCE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE 119E</t>
+          <t>ONE COMPETENCE 100E</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2564,17 +2564,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER 308E</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2626,22 +2626,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>ONE MODERN</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>ONE MODERN 083E</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2651,12 +2651,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2693,22 +2693,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>RDO ACE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>RDO ACE 2642E</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2827,22 +2827,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CONTI CONTESSA</t>
+          <t>HYUNDAI SUPREME</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>CONTI CONTESSA 027E</t>
+          <t>HYUNDAI SUPREME 160E</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2961,22 +2961,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>HYUNDAI FORCE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>HYUNDAI FORCE 119E</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -3028,22 +3028,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CTP</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>WAN HAI 331</t>
+          <t>HMM SOUTHAMPTON</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>WAN HAI 331 0030S</t>
+          <t>HMM SOUTHAMPTON 020W</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>59</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>MOL COURAGE</t>
+          <t>HMM VANCOUVER</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>MOL COURAGE 069E</t>
+          <t>HMM VANCOUVER 308E</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -3229,22 +3229,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE 100E</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -3296,22 +3296,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME</t>
+          <t>CONTI CONTESSA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME 160E</t>
+          <t>CONTI CONTESSA 027E</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -3363,22 +3363,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>CTP</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON</t>
+          <t>WAN HAI 331</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON 020W</t>
+          <t>WAN HAI 331 0030S</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>65</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-19 03:54 UTC</t>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -3430,47 +3430,114 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>FE3</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>HMM GDANSK</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>HMM GDANSK 020W</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>LA SPEZIA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>TRANSSHIPMENT (1)</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-10-20 04:06 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CNTAO→ITSPE</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ITSPE</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>QINGDAO, SHANDONG</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>PN3</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>ONE MODERN</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>ONE MODERN 083E</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>YM WEALTH</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>YM WEALTH 194E</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
         <is>
           <t>LA SPEZIA</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2027-01-21</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>2026-10-19 03:54 UTC</t>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-10-20 04:06 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -585,22 +585,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS 2642W</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MSC AINO</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>MSC AINO FI641A</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -786,22 +786,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>SAO PAULO EXPRESS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>SAO PAULO EXPRESS 2642W</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>51</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2027-01-06</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -987,22 +987,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>SAO PAULO EXPRESS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>SAO PAULO EXPRESS 2642W</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>54</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1255,22 +1255,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MSC AINO</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>MSC AINO FI641A</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>54</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1523,22 +1523,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS 2642W</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>47</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1657,22 +1657,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1697,45 +1697,49 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>HKHKG→NOOSL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>NOOSL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>JSM</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1745,12 +1749,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>53</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1760,7 +1764,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1791,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1808,12 +1812,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1823,7 +1827,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1854,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1871,12 +1875,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>47</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1886,7 +1890,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1917,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1934,12 +1938,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1949,7 +1953,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1997,22 +2001,22 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2043,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2060,12 +2064,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2075,7 +2079,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2102,18 +2106,18 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2123,12 +2127,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2138,7 +2142,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2165,18 +2169,18 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2186,12 +2190,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2201,7 +2205,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2253,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2264,74 +2268,70 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CNTAO→ITSPE</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ITSPE</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>QINGDAO, SHANDONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>PN3</t>
-        </is>
-      </c>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>MOL COURAGE</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>MOL COURAGE 069E</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>ROTTERDAM</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>47</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (1)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2363,17 +2363,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>MOL CHARISMA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>MOL CHARISMA 239E</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2425,22 +2425,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE</t>
+          <t>ONE MODERN</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE 100E</t>
+          <t>ONE MODERN 083E</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON 020W</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2559,22 +2559,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>RDO ACE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>RDO ACE 2642E</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>87</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2626,22 +2626,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>ONE MODERN</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>ONE MODERN 083E</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2651,12 +2651,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>RDO ACE</t>
+          <t>ONE SYMPHONY</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>RDO ACE 2642E</t>
+          <t>ONE SYMPHONY 2643E</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>79</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2760,22 +2760,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HMM IVY</t>
+          <t>HYUNDAI SUPREME</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>HMM IVY 006E</t>
+          <t>HYUNDAI SUPREME 160E</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2827,22 +2827,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME 160E</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2899,17 +2899,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY</t>
+          <t>HYUNDAI FORCE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY 2643E</t>
+          <t>HYUNDAI FORCE 119E</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>81</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE</t>
+          <t>HMM IVY</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE 119E</t>
+          <t>HMM IVY 006E</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>71</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON 020W</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER</t>
+          <t>YM WEALTH</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER 308E</t>
+          <t>YM WEALTH 194E</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>65</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>MOL CHARISMA</t>
+          <t>HMM VANCOUVER</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>MOL CHARISMA 239E</t>
+          <t>HMM VANCOUVER 308E</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>84</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>HMM SOUTHAMPTON</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>HMM SOUTHAMPTON 020W</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>CONTI CONTESSA</t>
+          <t>ONE COMPETENCE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>CONTI CONTESSA 027E</t>
+          <t>ONE COMPETENCE 100E</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -3363,22 +3363,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CTP</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>WAN HAI 331</t>
+          <t>HMM SOUTHAMPTON</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>WAN HAI 331 0030S</t>
+          <t>HMM SOUTHAMPTON 020W</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -3430,22 +3430,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>MOL COURAGE</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>MOL COURAGE 069E</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>70</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -3497,22 +3497,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>YM WEALTH</t>
+          <t>CONTI CONTESSA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>YM WEALTH 194E</t>
+          <t>CONTI CONTESSA 027E</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-20 04:06 UTC</t>
+          <t>2026-10-21 03:55 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -528,12 +528,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2027-01-06</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -595,12 +595,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -719,22 +719,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -786,22 +786,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS 2642W</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -863,12 +863,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>SAO PAULO EXPRESS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>SAO PAULO EXPRESS 2642W</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -987,22 +987,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS 2642W</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>54</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1389,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>53</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1533,12 +1533,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1590,22 +1590,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>SAO PAULO EXPRESS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>SAO PAULO EXPRESS 2642W</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>54</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1734,12 +1734,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1749,12 +1749,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1812,12 +1812,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>47</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1938,22 +1938,22 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2064,22 +2064,22 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>33</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2132,17 +2132,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2169,18 +2169,18 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>31</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2295,18 +2295,18 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2316,22 +2316,22 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>36</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2363,17 +2363,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>IAE</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MOL CHARISMA</t>
+          <t>SAN FRANCISCO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>MOL CHARISMA 239E</t>
+          <t>SAN FRANCISCO 009E</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>70</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2425,22 +2425,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ONE MODERN</t>
+          <t>CONTI CONTESSA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>ONE MODERN 083E</t>
+          <t>CONTI CONTESSA 027E</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>59</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2492,22 +2492,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>ONE SYMPHONY</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>ONE SYMPHONY 2643E</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2651,12 +2651,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2693,22 +2693,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY 2643E</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2785,12 +2785,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2894,22 +2894,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE</t>
+          <t>MOL CHARISMA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE 119E</t>
+          <t>MOL CHARISMA 239E</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2961,22 +2961,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HMM IVY</t>
+          <t>HMM SOUTHAMPTON</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>HMM IVY 006E</t>
+          <t>HMM SOUTHAMPTON 020W</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>59</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -3095,22 +3095,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>YM WEALTH</t>
+          <t>HMM SOUTHAMPTON</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>YM WEALTH 194E</t>
+          <t>HMM SOUTHAMPTON 020W</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>
@@ -3162,22 +3162,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER</t>
+          <t>ONE COMPETENCE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER 308E</t>
+          <t>ONE COMPETENCE 100E</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3202,342 +3202,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-21 03:55 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>FE3</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>HMM SOUTHAMPTON</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>HMM SOUTHAMPTON 020W</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2027-01-21</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2026-10-21 03:55 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2026-11-07</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>AX4</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>ONE COMPETENCE</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>ONE COMPETENCE 100E</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2027-01-21</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>2026-10-21 03:55 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>FE3</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>HMM SOUTHAMPTON</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>HMM SOUTHAMPTON 020W</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2026-12-28</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>2026-10-21 03:55 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>PN3</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>MOL COURAGE</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>MOL COURAGE 069E</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2027-01-21</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>2026-10-21 03:55 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>AX4</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>CONTI CONTESSA</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>CONTI CONTESSA 027E</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2027-01-21</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>2026-10-21 03:55 UTC</t>
+          <t>2026-10-22 03:55 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,22 +518,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -595,12 +595,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -719,22 +719,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -853,22 +853,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS 2642W</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2027-01-06</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -893,14 +893,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HKHKG→SEGOT</t>
+          <t>HKHKG→NOOSL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SEGOT</t>
+          <t>NOOSL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -930,27 +930,27 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>GOTHENBURG</t>
+          <t>ROTTERDAM</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>53</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1255,22 +1255,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1389,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>54</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1533,12 +1533,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1590,22 +1590,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>SAO PAULO EXPRESS 2642W</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>61</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1630,49 +1630,45 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>JSM</t>
-        </is>
-      </c>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1682,12 +1678,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>34</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1697,49 +1693,45 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>JSM</t>
-        </is>
-      </c>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1749,22 +1741,22 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1783,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1812,22 +1804,22 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1846,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1875,12 +1867,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1890,7 +1882,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1938,12 +1930,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1953,7 +1945,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1972,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -2001,22 +1993,22 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>47</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2043,18 +2035,18 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2064,12 +2056,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>36</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2079,7 +2071,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2098,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2127,22 +2119,22 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>33</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2161,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -2190,12 +2182,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2205,133 +2197,141 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>AX3</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>ONE SYMPHONY</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>ONE SYMPHONY 2643E</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>2026-11-08</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>PN3</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
+          <t>HYUNDAI SUPREME</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
+          <t>HYUNDAI SUPREME 160E</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>71</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2358,22 +2358,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>IAE</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO</t>
+          <t>MOL CHARISMA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO 009E</t>
+          <t>MOL CHARISMA 239E</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2450,12 +2450,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2492,22 +2492,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY</t>
+          <t>HMM SOUTHAMPTON</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY 2643E</t>
+          <t>HMM SOUTHAMPTON 020W</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2559,22 +2559,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>RDO ACE</t>
+          <t>ONE COMPETENCE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>RDO ACE 2642E</t>
+          <t>ONE COMPETENCE 100E</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2626,22 +2626,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>RDO ACE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>RDO ACE 2642E</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2760,22 +2760,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>IAE</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME</t>
+          <t>SAN FRANCISCO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME 160E</t>
+          <t>SAN FRANCISCO 009E</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>HMM SOUTHAMPTON</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>HMM SOUTHAMPTON 020W</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2894,22 +2894,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MOL CHARISMA</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>MOL CHARISMA 239E</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON 020W</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>55</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3028,22 +3028,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>MOL COURAGE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>MOL COURAGE 069E</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON 020W</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3162,22 +3162,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE</t>
+          <t>HMM HELSINKI</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE 100E</t>
+          <t>HMM HELSINKI 020W</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3202,7 +3202,74 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-22 03:55 UTC</t>
+          <t>2026-10-23 03:59 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CNTAO→ITSPE</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ITSPE</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>QINGDAO, SHANDONG</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>FE3</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>HMM HELSINKI</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>HMM HELSINKI 020W</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>LA SPEZIA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2027-01-18</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>TRANSSHIPMENT (1)</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-10-23 03:59 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -518,22 +518,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>52</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -719,22 +719,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -863,12 +863,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>61</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1255,22 +1255,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1322,22 +1322,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1533,12 +1533,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>51</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>52</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1657,18 +1657,18 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1741,22 +1741,22 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1867,22 +1867,22 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>33</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1993,12 +1993,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2035,18 +2035,18 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2056,22 +2056,22 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2119,22 +2119,22 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -2182,12 +2182,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2224,22 +2224,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY</t>
+          <t>YM WEALTH</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY 2643E</t>
+          <t>YM WEALTH 194E</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2291,22 +2291,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME 160E</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2363,17 +2363,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MOL CHARISMA</t>
+          <t>ONE COMPETENCE</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>MOL CHARISMA 239E</t>
+          <t>ONE COMPETENCE 100E</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2425,22 +2425,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>IAE</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CONTI CONTESSA</t>
+          <t>SAN FRANCISCO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>CONTI CONTESSA 027E</t>
+          <t>SAN FRANCISCO 009E</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON 020W</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2559,22 +2559,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE</t>
+          <t>SEASPAN ZAMBEZI</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE 100E</t>
+          <t>SEASPAN ZAMBEZI 2645E</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>69</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2760,22 +2760,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>IAE</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO</t>
+          <t>HMM SOUTHAMPTON</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO 009E</t>
+          <t>HMM SOUTHAMPTON 020W</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2827,22 +2827,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON</t>
+          <t>MOL COURAGE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON 020W</t>
+          <t>MOL COURAGE 069E</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>70</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2894,22 +2894,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>CONTI CONTESSA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>CONTI CONTESSA 027E</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2961,22 +2961,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>MOL CHARISMA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>MOL CHARISMA 239E</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>75</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3028,22 +3028,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>MOL COURAGE</t>
+          <t>ONE SYMPHONY</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>MOL COURAGE 069E</t>
+          <t>ONE SYMPHONY 2643E</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>79</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3095,22 +3095,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>HYUNDAI SUPREME</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>HYUNDAI SUPREME 160E</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>HMM HELSINKI</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>HMM HELSINKI 020W</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>HMM HELSINKI</t>
+          <t>HMM SOUTHAMPTON</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>HMM HELSINKI 020W</t>
+          <t>HMM SOUTHAMPTON 020W</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-23 03:59 UTC</t>
+          <t>2026-10-24 03:53 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,22 +518,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -585,22 +585,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>ONE MAGDALENA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>ONE MAGDALENA 2644W</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -719,22 +719,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -863,12 +863,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>52</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -893,14 +893,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>HKHKG→SEGOT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>SEGOT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -930,27 +930,27 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>GOTHENBURG</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>52</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>52</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1630,45 +1630,49 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>HKHKG→NOOSL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>NOOSL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>JSM</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1678,12 +1682,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1693,45 +1697,49 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>HKHKG→NOOSL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>NOOSL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SX1</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>ONE MAGDALENA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>ONE MAGDALENA 2644W</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1741,12 +1749,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1756,7 +1764,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1791,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1804,22 +1812,22 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1854,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1867,12 +1875,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1882,7 +1890,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1917,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1930,22 +1938,22 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1980,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1998,17 +2006,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2043,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2056,22 +2064,22 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>33</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2098,18 +2106,18 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2119,22 +2127,22 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>36</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2169,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -2182,156 +2190,148 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CNTAO→ITSPE</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ITSPE</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>QINGDAO, SHANDONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>PN3</t>
-        </is>
-      </c>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>YM WEALTH</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>YM WEALTH 194E</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>ROTTERDAM</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (1)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CNTAO→ITSPE</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ITSPE</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>QINGDAO, SHANDONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>FE3</t>
-        </is>
-      </c>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>ROTTERDAM</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (1)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2358,22 +2358,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE</t>
+          <t>HMM SOUTHAMPTON</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE 100E</t>
+          <t>HMM SOUTHAMPTON 020W</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2425,22 +2425,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>IAE</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO</t>
+          <t>YM WEALTH</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO 009E</t>
+          <t>YM WEALTH 194E</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2559,22 +2559,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SEASPAN ZAMBEZI</t>
+          <t>HMM HELSINKI</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SEASPAN ZAMBEZI 2645E</t>
+          <t>HMM HELSINKI 020W</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-04</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2626,22 +2626,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>RDO ACE</t>
+          <t>ONE COMPETENCE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>RDO ACE 2642E</t>
+          <t>ONE COMPETENCE 100E</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2693,22 +2693,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>IAE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>SAN FRANCISCO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>SAN FRANCISCO 009E</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON 020W</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2827,22 +2827,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>MOL COURAGE</t>
+          <t>HMM HELSINKI</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>MOL COURAGE 069E</t>
+          <t>HMM HELSINKI 020W</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>59</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2894,22 +2894,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>CONTI CONTESSA</t>
+          <t>SEASPAN ZAMBEZI</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>CONTI CONTESSA 027E</t>
+          <t>SEASPAN ZAMBEZI 2645E</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -3028,22 +3028,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY 2643E</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>69</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME</t>
+          <t>MOL COURAGE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME 160E</t>
+          <t>MOL COURAGE 069E</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>70</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -3162,22 +3162,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>CONTI CONTESSA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>CONTI CONTESSA 027E</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-24 03:53 UTC</t>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>
@@ -3229,47 +3229,248 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>AX3</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ONE SYMPHONY</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>ONE SYMPHONY 2643E</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>LA SPEZIA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2027-01-21</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>TRANSSHIPMENT (1)</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-10-25 03:52 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CNTAO→ITSPE</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ITSPE</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>QINGDAO, SHANDONG</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-11-08</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>PN3</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>HYUNDAI SUPREME</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>HYUNDAI SUPREME 160E</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>LA SPEZIA</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2027-01-21</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>TRANSSHIPMENT (1)</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-10-25 03:52 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CNTAO→ITSPE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ITSPE</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>QINGDAO, SHANDONG</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>FE3</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>HMM GDANSK</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>HMM GDANSK 020W</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>LA SPEZIA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>TRANSSHIPMENT (1)</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-10-25 03:52 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CNTAO→ITSPE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ITSPE</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>QINGDAO, SHANDONG</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>2026-11-16</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>FE3</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>HMM SOUTHAMPTON</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>HMM SOUTHAMPTON 020W</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>LA SPEZIA</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>2027-01-21</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2026-10-24 03:53 UTC</t>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-10-25 03:52 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,22 +518,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -595,12 +595,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA 2644W</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>ONE MAGDALENA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>ONE MAGDALENA 2644W</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>54</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>52</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -863,12 +863,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -920,22 +920,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>CAPE ARTEMISIO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>CAPE ARTEMISIO FI645A</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -960,14 +960,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>HKHKG→SEGOT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>SEGOT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -997,27 +997,27 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>GOTHENBURG</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -1188,22 +1188,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>CAPE ARTEMISIO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>CAPE ARTEMISIO FI645A</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>52</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>ONE MAGDALENA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>ONE MAGDALENA 2644W</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>52</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -1724,22 +1724,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA 2644W</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1749,12 +1749,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1764,45 +1764,49 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>HKHKG→NOOSL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>NOOSL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>JSM</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1812,60 +1816,64 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>HKHKG→NOOSL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>NOOSL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SX1</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1875,12 +1883,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1890,7 +1898,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1925,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1938,7 +1946,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1953,7 +1961,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1988,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -2001,12 +2009,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2016,7 +2024,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2087,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -2106,18 +2114,18 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN GIANG NAM LOGISTICS (WATER)</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2127,22 +2135,22 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2177,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -2190,22 +2198,22 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2240,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -2258,7 +2266,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2268,7 +2276,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2303,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -2316,12 +2324,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2331,74 +2339,70 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CNTAO→ITSPE</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ITSPE</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>QINGDAO, SHANDONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>FE3</t>
-        </is>
-      </c>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON 020W</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>ROTTERDAM</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (1)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -2425,22 +2429,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>YM WEALTH</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>YM WEALTH 194E</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2450,12 +2454,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2465,7 +2469,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2536,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -2559,22 +2563,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>HMM HELSINKI</t>
+          <t>YM WEALTH</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>HMM HELSINKI 020W</t>
+          <t>YM WEALTH 194E</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2584,12 +2588,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2599,7 +2603,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -2626,22 +2630,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE</t>
+          <t>SEASPAN ZAMBEZI</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE 100E</t>
+          <t>SEASPAN ZAMBEZI 2645E</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2651,12 +2655,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2666,7 +2670,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -2693,22 +2697,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>IAE</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO</t>
+          <t>MOL CHARISMA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO 009E</t>
+          <t>MOL CHARISMA 239E</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2723,7 +2727,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2733,7 +2737,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -2785,12 +2789,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>69</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2800,7 +2804,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -2827,22 +2831,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HMM HELSINKI</t>
+          <t>CONTI CONTESSA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>HMM HELSINKI 020W</t>
+          <t>CONTI CONTESSA 027E</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2857,7 +2861,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2867,7 +2871,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -2894,22 +2898,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SEASPAN ZAMBEZI</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>SEASPAN ZAMBEZI 2645E</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2919,12 +2923,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2934,7 +2938,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -2966,17 +2970,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>MOL CHARISMA</t>
+          <t>ONE COMPETENCE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>MOL CHARISMA 239E</t>
+          <t>ONE COMPETENCE 100E</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2991,7 +2995,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3001,7 +3005,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -3028,22 +3032,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>IAE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>SAN FRANCISCO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>SAN FRANCISCO 009E</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3053,12 +3057,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3068,7 +3072,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -3095,22 +3099,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>MOL COURAGE</t>
+          <t>ONE SYMPHONY</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>MOL COURAGE 069E</t>
+          <t>ONE SYMPHONY 2643E</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3125,7 +3129,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>79</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3135,7 +3139,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -3162,22 +3166,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>CONTI CONTESSA</t>
+          <t>HYUNDAI SUPREME</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>CONTI CONTESSA 027E</t>
+          <t>HYUNDAI SUPREME 160E</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3192,7 +3196,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3202,7 +3206,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -3229,22 +3233,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY</t>
+          <t>MOL COURAGE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY 2643E</t>
+          <t>MOL COURAGE 069E</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3259,7 +3263,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>69</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3269,7 +3273,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -3296,22 +3300,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME</t>
+          <t>HMM SOUTHAMPTON</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME 160E</t>
+          <t>HMM SOUTHAMPTON 020W</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3326,7 +3330,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3336,7 +3340,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3367,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3373,12 +3377,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>HMM SOUTHAMPTON</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>HMM SOUTHAMPTON 020W</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3388,12 +3392,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3403,7 +3407,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3434,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3440,12 +3444,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON</t>
+          <t>HMM HELSINKI</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON 020W</t>
+          <t>HMM HELSINKI 020W</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3460,7 +3464,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>59</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3470,7 +3474,74 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-25 03:52 UTC</t>
+          <t>2026-10-26 03:56 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CNTAO→ITSPE</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ITSPE</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>QINGDAO, SHANDONG</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-11-22</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>FE3</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>HMM HELSINKI</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>HMM HELSINKI 020W</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>LA SPEZIA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2027-01-04</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>TRANSSHIPMENT (1)</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-10-26 03:56 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,22 +518,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -585,22 +585,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>52</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA 2644W</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -786,22 +786,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>CAPE ARTEMISIO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>CAPE ARTEMISIO FI645A</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -853,22 +853,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>ONE MAGDALENA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>ONE MAGDALENA 2644W</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -920,22 +920,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CAPE ARTEMISIO</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CAPE ARTEMISIO FI645A</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -1121,22 +1121,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>ONE MAGDALENA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>ONE MAGDALENA 2644W</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -1188,22 +1188,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CAPE ARTEMISIO</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CAPE ARTEMISIO FI645A</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA 2644W</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>CAPE ARTEMISIO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>CAPE ARTEMISIO FI645A</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -1548,12 +1548,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>52</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1734,12 +1734,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1749,12 +1749,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1816,12 +1816,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -1858,22 +1858,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>52</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1946,12 +1946,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2072,12 +2072,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -2135,22 +2135,22 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -2198,22 +2198,22 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -2521,12 +2521,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -2630,22 +2630,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SEASPAN ZAMBEZI</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SEASPAN ZAMBEZI 2645E</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2655,12 +2655,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>62</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>MOL CHARISMA</t>
+          <t>SEASPAN ZAMBEZI</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>MOL CHARISMA 239E</t>
+          <t>SEASPAN ZAMBEZI 2645E</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>61</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -2764,22 +2764,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>MOL CHARISMA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>MOL CHARISMA 239E</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -2831,22 +2831,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CONTI CONTESSA</t>
+          <t>ONE SYMPHONY</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>CONTI CONTESSA 027E</t>
+          <t>ONE SYMPHONY 2643E</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>78</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -2898,22 +2898,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>CONTI CONTESSA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>CONTI CONTESSA 027E</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -2965,22 +2965,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>MS2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE</t>
+          <t>ONE SYNERGY</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE 100E</t>
+          <t>ONE SYNERGY 003W</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2995,17 +2995,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>57</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (1)</t>
+          <t>DIRECT (0)</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -3032,22 +3032,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>IAE</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO</t>
+          <t>ONE COMPETENCE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO 009E</t>
+          <t>ONE COMPETENCE 100E</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -3099,22 +3099,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>IAE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY</t>
+          <t>SAN FRANCISCO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY 2643E</t>
+          <t>SAN FRANCISCO 009E</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3377,12 +3377,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON 020W</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3444,12 +3444,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>HMM HELSINKI</t>
+          <t>HMM SOUTHAMPTON</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>HMM HELSINKI 020W</t>
+          <t>HMM SOUTHAMPTON 020W</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3459,12 +3459,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-26 03:56 UTC</t>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -3526,22 +3526,89 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t>2027-01-21</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>TRANSSHIPMENT (1)</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-10-27 04:18 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CNTAO→ITSPE</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ITSPE</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>QINGDAO, SHANDONG</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-11-22</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>FE3</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>HMM HELSINKI</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>HMM HELSINKI 020W</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>LA SPEZIA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
           <t>2027-01-04</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>2026-10-26 03:56 UTC</t>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-10-27 04:18 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,22 +518,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -585,22 +585,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>CAPE ARTEMISIO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>CAPE ARTEMISIO FI645A</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>NAVIOS CHRYSALIS 019S</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -719,22 +719,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -791,17 +791,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CAPE ARTEMISIO</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CAPE ARTEMISIO FI645A</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -853,22 +853,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA 2644W</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -987,22 +987,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>ONE MAGDALENA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>ONE MAGDALENA 2644W</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1027,14 +1027,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>HKHKG→SEGOT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>SEGOT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1064,27 +1064,27 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>GOTHENBURG</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1121,22 +1121,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA 2644W</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>NAVIOS CHRYSALIS 019S</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>CAPE ARTEMISIO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>CAPE ARTEMISIO FI645A</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>52</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CAPE ARTEMISIO</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>CAPE ARTEMISIO FI645A</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>52</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1590,22 +1590,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1749,12 +1749,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1791,22 +1791,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>ONE MAGDALENA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>ONE MAGDALENA 2644W</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1816,12 +1816,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>51</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1898,45 +1898,49 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>HKHKG→NOOSL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>NOOSL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>JSM</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1946,12 +1950,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1961,45 +1965,49 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>HKHKG→NOOSL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>NOOSL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>JSM</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2009,12 +2017,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>61</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2024,45 +2032,49 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>HKHKG→NOOSL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>NOOSL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>JSM</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>NAVIOS CHRYSALIS 019S</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2072,12 +2084,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>54</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2087,7 +2099,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2126,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2140,17 +2152,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2225,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2252,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -2261,12 +2273,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2276,7 +2288,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2315,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -2329,17 +2341,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>32</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2378,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -2387,178 +2399,170 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CNTAO→ITSPE</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ITSPE</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>QINGDAO, SHANDONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>FE3</t>
-        </is>
-      </c>
+          <t>2026-11-15</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>ROTTERDAM</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (1)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CNTAO→ITSPE</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ITSPE</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>QINGDAO, SHANDONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>FE3</t>
-        </is>
-      </c>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>ROTTERDAM</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>32</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (1)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CNTAO→ITSPE</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ITSPE</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>QINGDAO, SHANDONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2566,44 +2570,40 @@
           <t>2026-11-17</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>PN3</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>YM WEALTH</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>YM WEALTH 194E</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>ROTTERDAM</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (1)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2630,22 +2630,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>HYUNDAI SUPREME</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>HYUNDAI SUPREME 160E</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2655,12 +2655,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>78</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SEASPAN ZAMBEZI</t>
+          <t>CONTI CONTESSA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SEASPAN ZAMBEZI 2645E</t>
+          <t>CONTI CONTESSA 027E</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>70</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2764,22 +2764,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>IAE</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>MOL CHARISMA</t>
+          <t>SAN FRANCISCO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>MOL CHARISMA 239E</t>
+          <t>SAN FRANCISCO 009E</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>81</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2831,22 +2831,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY</t>
+          <t>HYUNDAI FORWARD</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY 2643E</t>
+          <t>HYUNDAI FORWARD 173E</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2856,12 +2856,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-02-05</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>71</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2898,22 +2898,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>CONTI CONTESSA</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>CONTI CONTESSA 027E</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2965,22 +2965,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MS2</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>ONE SYNERGY</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>ONE SYNERGY 003W</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2990,22 +2990,22 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>DIRECT (0)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3032,22 +3032,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE</t>
+          <t>HMM SOUTHAMPTON</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE 100E</t>
+          <t>HMM SOUTHAMPTON 020W</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>70</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3099,22 +3099,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>IAE</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO</t>
+          <t>ONE SYMPHONY</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO 009E</t>
+          <t>ONE SYMPHONY 2643E</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>82</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME</t>
+          <t>YM WEALTH</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME 160E</t>
+          <t>YM WEALTH 194E</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>69</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3233,22 +3233,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>MOL COURAGE</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>MOL COURAGE 069E</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>62</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON 020W</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3377,12 +3377,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>HMM HELSINKI</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>HMM HELSINKI 020W</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3434,22 +3434,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON</t>
+          <t>SEASPAN ZAMBEZI</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON 020W</t>
+          <t>SEASPAN ZAMBEZI 2645E</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3459,12 +3459,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>65</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3501,22 +3501,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>HMM HELSINKI</t>
+          <t>MOL CHARISMA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>HMM HELSINKI 020W</t>
+          <t>MOL CHARISMA 239E</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>78</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-27 04:18 UTC</t>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3578,37 +3578,238 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
+          <t>HMM SOUTHAMPTON</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>HMM SOUTHAMPTON 020W</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>LA SPEZIA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-12-28</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>TRANSSHIPMENT (1)</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-10-28 04:47 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CNTAO→ITSPE</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ITSPE</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>QINGDAO, SHANDONG</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>AX4</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>HYUNDAI FORCE</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>HYUNDAI FORCE 119E</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>LA SPEZIA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>TRANSSHIPMENT (1)</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-10-28 04:47 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CNTAO→ITSPE</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ITSPE</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>QINGDAO, SHANDONG</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>FE3</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
           <t>HMM HELSINKI</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>HMM HELSINKI 020W</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>LA SPEZIA</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2027-01-04</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-12-28</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>2026-10-27 04:18 UTC</t>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-10-28 04:47 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>CNTAO→ITSPE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ITSPE</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>QINGDAO, SHANDONG</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>PN3</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>MOL COURAGE</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>MOL COURAGE 069E</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>LA SPEZIA</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2027-01-25</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>TRANSSHIPMENT (1)</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-10-28 04:47 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -528,12 +528,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CAPE ARTEMISIO</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CAPE ARTEMISIO FI645A</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 019S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>ONE MAGDALENA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>ONE MAGDALENA 2644W</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -863,12 +863,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -920,22 +920,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA</t>
+          <t>CAPE ARTEMISIO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA 2644W</t>
+          <t>CAPE ARTEMISIO FI645A</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>52</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1027,14 +1027,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HKHKG→SEGOT</t>
+          <t>HKHKG→NOOSL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SEGOT</t>
+          <t>NOOSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1074,17 +1074,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>GOTHENBURG</t>
+          <t>ROTTERDAM</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>51</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1121,22 +1121,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 019S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1590,22 +1590,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>61</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1657,22 +1657,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>ONE MAGDALENA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>ONE MAGDALENA 2644W</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1734,12 +1734,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1749,12 +1749,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1791,22 +1791,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA 2644W</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1816,12 +1816,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1898,49 +1898,45 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>JSM</t>
-        </is>
-      </c>
+          <t>2026-11-22</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1950,12 +1946,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>33</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1965,49 +1961,45 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>JSM</t>
-        </is>
-      </c>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2017,12 +2009,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>32</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2032,49 +2024,45 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>JSM</t>
-        </is>
-      </c>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 019S</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2084,22 +2072,22 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2114,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2147,12 +2135,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2162,7 +2150,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2177,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -2210,12 +2198,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2225,7 +2213,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2240,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -2273,22 +2261,22 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2303,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -2336,22 +2324,22 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2378,7 +2366,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -2404,17 +2392,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2450,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2477,133 +2465,141 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>PN3</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>HYUNDAI SUPREME</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>HYUNDAI SUPREME 160E</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>78</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>AX4</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>CONTI CONTESSA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>CONTI CONTESSA 027E</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>70</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2630,22 +2626,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>IAE</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME</t>
+          <t>SAN FRANCISCO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME 160E</t>
+          <t>SAN FRANCISCO 009E</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2660,7 +2656,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>81</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2670,7 +2666,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2693,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>CONTI CONTESSA</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>CONTI CONTESSA 027E</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2722,12 +2718,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2737,7 +2733,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2769,17 +2765,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>IAE</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO 009E</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2789,12 +2785,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2804,7 +2800,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2831,22 +2827,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HYUNDAI FORWARD</t>
+          <t>HMM SOUTHAMPTON</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>HYUNDAI FORWARD 173E</t>
+          <t>HMM SOUTHAMPTON 020W</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2856,12 +2852,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2027-02-05</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>70</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2871,7 +2867,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2898,22 +2894,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>ONE SYMPHONY</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>ONE SYMPHONY 2643E</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2923,12 +2919,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>82</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2938,7 +2934,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2965,22 +2961,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>YM WEALTH</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>YM WEALTH 194E</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2990,12 +2986,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>69</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3005,7 +3001,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3057,12 +3053,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3072,7 +3068,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3099,22 +3095,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY</t>
+          <t>MOL COURAGE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY 2643E</t>
+          <t>MOL COURAGE 069E</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3129,7 +3125,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>73</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3139,7 +3135,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3166,22 +3162,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>YM WEALTH</t>
+          <t>HMM HELSINKI</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>YM WEALTH 194E</t>
+          <t>HMM HELSINKI 020W</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3191,12 +3187,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-04</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3206,7 +3202,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3233,22 +3229,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>MOL CHARISMA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>MOL CHARISMA 239E</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3258,12 +3254,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>78</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3273,7 +3269,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3300,22 +3296,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>HYUNDAI FORWARD</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>HYUNDAI FORWARD 173E</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3325,12 +3321,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2027-02-04</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>71</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3340,7 +3336,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3372,17 +3368,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>HMM HELSINKI</t>
+          <t>SEASPAN ZAMBEZI</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>HMM HELSINKI 020W</t>
+          <t>SEASPAN ZAMBEZI 2645E</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3397,7 +3393,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3407,7 +3403,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3434,22 +3430,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SEASPAN ZAMBEZI</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>SEASPAN ZAMBEZI 2645E</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3459,12 +3455,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>62</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3474,7 +3470,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3501,22 +3497,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>MOL CHARISMA</t>
+          <t>HMM HELSINKI</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>MOL CHARISMA 239E</t>
+          <t>HMM HELSINKI 020W</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3531,7 +3527,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3541,7 +3537,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3568,22 +3564,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON</t>
+          <t>HYUNDAI FORCE</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON 020W</t>
+          <t>HYUNDAI FORCE 119E</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3593,12 +3589,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3608,7 +3604,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3635,22 +3631,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE 119E</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3660,12 +3656,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3675,141 +3671,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-10-28 04:47 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2026-11-19</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>FE3</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>HMM HELSINKI</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>HMM HELSINKI 020W</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2026-12-28</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>2026-10-28 04:47 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>PN3</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>MOL COURAGE</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>MOL COURAGE 069E</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>2027-01-25</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>2026-10-28 04:47 UTC</t>
+          <t>2026-10-29 04:59 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,22 +518,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -595,12 +595,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -719,22 +719,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA 2644W</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -853,22 +853,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>ONE MAGDALENA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>ONE MAGDALENA 2644W</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -920,22 +920,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1054,22 +1054,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>CAPE ARTEMISIO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>CAPE ARTEMISIO FI645A</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1322,22 +1322,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CAPE ARTEMISIO</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CAPE ARTEMISIO FI645A</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>ONE MAGDALENA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>ONE MAGDALENA 2644W</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1657,22 +1657,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA 2644W</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>53</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1734,12 +1734,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1749,12 +1749,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1951,17 +1951,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -2009,12 +2009,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2140,17 +2140,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>33</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -2198,12 +2198,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -2261,12 +2261,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2339,133 +2339,141 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>PN3</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>HYUNDAI SUPREME</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>HYUNDAI SUPREME 160E</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>75</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>FE3</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>62</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2492,22 +2500,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME</t>
+          <t>YOKOHAMA EXPRESS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME 160E</t>
+          <t>YOKOHAMA EXPRESS 2646E</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2517,12 +2525,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>62</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2532,7 +2540,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2559,22 +2567,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CONTI CONTESSA</t>
+          <t>HMM ALGECIRAS</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>CONTI CONTESSA 027E</t>
+          <t>HMM ALGECIRAS 021W</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2584,12 +2592,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>36</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2599,7 +2607,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2626,22 +2634,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>IAE</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO</t>
+          <t>MOL COURAGE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO 009E</t>
+          <t>MOL COURAGE 069E</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2651,12 +2659,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>71</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2666,7 +2674,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2701,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2703,12 +2711,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>HMM HELSINKI</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>HMM HELSINKI 020W</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2718,12 +2726,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>64</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2733,7 +2741,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2768,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2770,12 +2778,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>HMM HELSINKI</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>HMM HELSINKI 020W</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2785,12 +2793,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-01-04</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2800,7 +2808,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2827,22 +2835,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON</t>
+          <t>HYUNDAI FORCE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON 020W</t>
+          <t>HYUNDAI FORCE 119E</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2852,12 +2860,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2867,7 +2875,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2894,22 +2902,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY</t>
+          <t>HMM SOUTHAMPTON</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY 2643E</t>
+          <t>HMM SOUTHAMPTON 020W</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2919,12 +2927,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2934,7 +2942,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2961,22 +2969,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>IAE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>YM WEALTH</t>
+          <t>SAN FRANCISCO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>YM WEALTH 194E</t>
+          <t>SAN FRANCISCO 009E</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2986,12 +2994,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>78</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3001,7 +3009,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3028,22 +3036,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON</t>
+          <t>YM WEALTH</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON 020W</t>
+          <t>YM WEALTH 194E</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3053,12 +3061,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>73</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3068,7 +3076,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3095,22 +3103,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>MOL COURAGE</t>
+          <t>ONE SYMPHONY</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>MOL COURAGE 069E</t>
+          <t>ONE SYMPHONY 2643E</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3120,12 +3128,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>79</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3135,7 +3143,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3167,17 +3175,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>HMM HELSINKI</t>
+          <t>SEASPAN ZAMBEZI</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>HMM HELSINKI 020W</t>
+          <t>SEASPAN ZAMBEZI 2645E</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3187,12 +3195,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3202,7 +3210,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3254,12 +3262,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3269,7 +3277,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3296,22 +3304,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HYUNDAI FORWARD</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>HYUNDAI FORWARD 173E</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3321,12 +3329,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2027-02-04</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3336,7 +3344,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3363,22 +3371,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SEASPAN ZAMBEZI</t>
+          <t>HMM HAMBURG</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>SEASPAN ZAMBEZI 2645E</t>
+          <t>HMM HAMBURG 020W</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3388,12 +3396,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-09</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3403,7 +3411,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3438,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3440,12 +3448,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>HMM HAMBURG</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>HMM HAMBURG 020W</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3455,12 +3463,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3470,7 +3478,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3497,22 +3505,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>HMM HELSINKI</t>
+          <t>HYUNDAI FORWARD</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>HMM HELSINKI 020W</t>
+          <t>HYUNDAI FORWARD 173E</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3522,12 +3530,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-02-04</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>71</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3537,7 +3545,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3564,22 +3572,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE 119E</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3589,12 +3597,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3604,7 +3612,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3639,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3641,12 +3649,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>HMM SOUTHAMPTON</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>HMM SOUTHAMPTON 020W</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3656,12 +3664,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3671,7 +3679,74 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-10-29 04:59 UTC</t>
+          <t>2026-10-30 04:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CNTAO→ITSPE</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ITSPE</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>QINGDAO, SHANDONG</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>AX4</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>CONTI CONTESSA</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>CONTI CONTESSA 027E</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>LA SPEZIA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2027-01-22</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>TRANSSHIPMENT (1)</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-10-30 04:58 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,22 +518,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SANTA CATARINA EXPRESS 2643W</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -585,22 +585,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>ONE MAGDALENA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>ONE MAGDALENA 2644W</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -719,22 +719,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>CAPE ARTEMISIO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>CAPE ARTEMISIO FI645A</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -853,22 +853,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA 2644W</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -920,22 +920,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>SANTA CATARINA EXPRESS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>SANTA CATARINA EXPRESS 2643W</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -987,22 +987,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CAPE ARTEMISIO</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CAPE ARTEMISIO FI645A</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CAPE ARTEMISIO</t>
+          <t>ONE MAGDALENA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CAPE ARTEMISIO FI645A</t>
+          <t>ONE MAGDALENA 2644W</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA 2644W</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1533,12 +1533,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 188S</t>
+          <t>ATHENS BRIDGE 1190S</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1590,22 +1590,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>CAPE ARTEMISIO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>EMMANUEL P 015S</t>
+          <t>CAPE ARTEMISIO FI645A</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1190S</t>
+          <t>EMMANUEL P 015S</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>NAVIOS VERDE 188S</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1749,12 +1749,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>51</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 189S</t>
+          <t>NAVIOS CHRYSALIS 018S</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1816,12 +1816,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 018S</t>
+          <t>NAVIOS VERDE 189S</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -2009,22 +2009,22 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2072,12 +2072,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2135,12 +2135,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -2198,12 +2198,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -2261,12 +2261,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -2324,22 +2324,22 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2366,22 +2366,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME</t>
+          <t>ONE SYMPHONY</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME 160E</t>
+          <t>ONE SYMPHONY 2643E</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>78</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>HMM HAMBURG</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>HMM HAMBURG 020W</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2458,12 +2458,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2500,22 +2500,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>YOKOHAMA EXPRESS</t>
+          <t>HYUNDAI FORWARD</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>YOKOHAMA EXPRESS 2646E</t>
+          <t>HYUNDAI FORWARD 173E</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2027-02-13</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>79</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2577,12 +2577,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS</t>
+          <t>HMM HELSINKI</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>HMM ALGECIRAS 021W</t>
+          <t>HMM HELSINKI 020W</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>64</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MOL COURAGE</t>
+          <t>YM WEALTH</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>MOL COURAGE 069E</t>
+          <t>YM WEALTH 194E</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2726,12 +2726,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-04</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HMM HELSINKI</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>HMM HELSINKI 020W</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2835,22 +2835,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE</t>
+          <t>MOL CHARISMA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>HYUNDAI FORCE 119E</t>
+          <t>MOL CHARISMA 239E</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2902,22 +2902,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON</t>
+          <t>HYUNDAI FORCE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>HMM SOUTHAMPTON 020W</t>
+          <t>HYUNDAI FORCE 119E</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2969,22 +2969,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>IAE</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO</t>
+          <t>HMM SOUTHAMPTON</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO 009E</t>
+          <t>HMM SOUTHAMPTON 020W</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3036,22 +3036,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>YM WEALTH</t>
+          <t>HMM SOUTHAMPTON</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>YM WEALTH 194E</t>
+          <t>HMM SOUTHAMPTON 020W</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3103,22 +3103,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>IAE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY</t>
+          <t>SAN FRANCISCO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>ONE SYMPHONY 2643E</t>
+          <t>SAN FRANCISCO 009E</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>78</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3170,22 +3170,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SEASPAN ZAMBEZI</t>
+          <t>MOL COURAGE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SEASPAN ZAMBEZI 2645E</t>
+          <t>MOL COURAGE 069E</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>71</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>MOL CHARISMA</t>
+          <t>HYUNDAI SUPREME</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>MOL CHARISMA 239E</t>
+          <t>HYUNDAI SUPREME 160E</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HMM GDANSK</t>
+          <t>HMM HAMBURG</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>HMM GDANSK 020W</t>
+          <t>HMM HAMBURG 020W</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-01-11</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3371,22 +3371,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>HMM HAMBURG</t>
+          <t>SEASPAN ZAMBEZI</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>HMM HAMBURG 020W</t>
+          <t>SEASPAN ZAMBEZI 2645E</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>HMM HAMBURG</t>
+          <t>HMM GDANSK</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>HMM HAMBURG 020W</t>
+          <t>HMM GDANSK 020W</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3505,22 +3505,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>HYUNDAI FORWARD</t>
+          <t>YOKOHAMA EXPRESS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>HYUNDAI FORWARD 173E</t>
+          <t>YOKOHAMA EXPRESS 2646E</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2027-02-04</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>62</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3545,208 +3545,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>FE3</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>HMM GDANSK</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>HMM GDANSK 020W</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2026-12-11</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>2026-10-30 04:58 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>FE3</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>HMM SOUTHAMPTON</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>HMM SOUTHAMPTON 020W</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2027-01-22</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>2026-10-30 04:58 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>AX4</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>CONTI CONTESSA</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>CONTI CONTESSA 027E</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2027-01-22</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>2026-10-30 04:58 UTC</t>
+          <t>2026-10-31 04:45 UTC</t>
         </is>
       </c>
     </row>
